--- a/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
@@ -627,7 +627,7 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -645,7 +645,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -669,14 +669,13 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M4" s="2" t="n"/>
@@ -692,10 +691,14 @@
 </t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">2150
 </t>
         </is>
       </c>
@@ -707,7 +710,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -719,7 +722,7 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -731,7 +734,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>16</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -742,10 +745,16 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="n"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -758,7 +767,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5082
+</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -774,111 +788,121 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">615
+</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1146
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10920
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">619
-</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="n"/>
-      <c r="Y5" s="2" t="n"/>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -896,13 +920,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">22441
 </t>
         </is>
       </c>
@@ -914,7 +938,8 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -925,7 +950,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -937,102 +962,97 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1318
+</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1436
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591
+</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0920
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11458
-</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">591
-</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1050,7 +1070,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -1062,18 +1082,19 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -1085,67 +1106,68 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">9837
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">7181
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1776
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1156,7 +1178,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -1168,25 +1190,25 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -1204,7 +1226,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1222,72 +1244,67 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1959
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -1299,49 +1316,49 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1359,75 +1376,80 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">11835
+</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6156
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n"/>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t xml:space="preserve">631
+</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t xml:space="preserve">164
+</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">17179190
+1
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">659
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">1738
 </t>
         </is>
       </c>
@@ -1438,41 +1460,46 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t xml:space="preserve">30
+</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr"/>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1490,7 +1517,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1507,35 +1534,40 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">102
 </t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1550,14 +1582,13 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1568,31 +1599,31 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1610,19 +1641,19 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10884
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1640,12 +1671,13 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t xml:space="preserve">2989
+</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1663,12 +1695,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1679,37 +1712,38 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">14686
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,62 +1754,60 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">22
+198
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1638
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,21 +1822,16 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2295
-</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -1816,73 +1843,73 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1091
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -1894,13 +1921,13 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -1918,18 +1945,20 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,13 +1975,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293220
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">636
 </t>
         </is>
       </c>
@@ -1970,7 +1999,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
@@ -1982,17 +2011,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">150
@@ -2007,78 +2036,74 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>9464</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1582
+</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1685
+</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2094,12 +2119,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3240
-</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">218
@@ -2108,7 +2128,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2120,19 +2140,19 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2142,7 +2162,12 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="2" t="n"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">144
@@ -2157,20 +2182,25 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1583
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">1413
 </t>
         </is>
       </c>
@@ -2182,19 +2212,19 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1712
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2212,19 +2242,19 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2242,37 +2272,41 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
+          <t xml:space="preserve">14755
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n"/>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
@@ -2284,37 +2318,26 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">968
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2331,13 +2354,13 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">3730
 </t>
         </is>
       </c>
@@ -2361,19 +2384,19 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8855
+          <t xml:space="preserve">3410
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2391,19 +2414,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14259
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2413,13 +2436,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11074
+          <t xml:space="preserve">474
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2429,83 +2452,93 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">732
 </t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="n"/>
+          <t xml:space="preserve">5117
+18
+</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>234</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t xml:space="preserve">880
+</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">39945
+</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1845
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>256</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2523,25 +2556,25 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">1343
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1481
 </t>
         </is>
       </c>
@@ -2553,55 +2586,54 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">746
-</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -2619,41 +2651,43 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -2671,19 +2705,18 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
+          <t xml:space="preserve">4285
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -2695,19 +2728,30 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2718,35 +2762,38 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">920
+</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2767,26 +2814,23 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2803,7 +2847,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4285
+          <t xml:space="preserve">4406
 </t>
         </is>
       </c>
@@ -2821,19 +2865,19 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1952
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -2845,13 +2889,13 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -2863,25 +2907,21 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112
+7
+</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2899,48 +2939,50 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1672
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">8105
+</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">44
+</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2957,31 +2999,31 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">769
 </t>
         </is>
       </c>
@@ -2992,15 +3034,10 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -3012,55 +3049,51 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -3072,19 +3105,19 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3102,25 +3135,25 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">24617
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2419
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3132,11 +3165,16 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -3145,7 +3183,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3163,20 +3201,25 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2414
 </t>
         </is>
       </c>
@@ -3194,13 +3237,13 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">748
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3212,24 +3255,25 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3247,19 +3291,19 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2066
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3271,92 +3315,86 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1125
-</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n"/>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1178
-</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">562
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3366,21 +3404,16 @@
 </t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
+      <c r="X22" s="2" t="n"/>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3398,7 +3431,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">1477
 </t>
         </is>
       </c>
@@ -3408,11 +3441,14 @@
 </t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3421,23 +3457,15 @@
 </t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>6170</t>
-        </is>
-      </c>
+      <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>33211</t>
-        </is>
-      </c>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">762
@@ -3447,25 +3475,25 @@
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
+          <t xml:space="preserve">1798
 </t>
         </is>
       </c>
@@ -3483,7 +3511,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>419</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3494,25 +3522,29 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="n"/>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4995
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3529,8 +3561,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14779
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3541,7 +3572,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3553,15 +3584,11 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -3573,15 +3600,10 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3591,27 +3613,18 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+111
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3623,13 +3636,13 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3647,25 +3660,26 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3682,84 +3696,80 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>961</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>146</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>901</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3781,25 +3791,25 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3817,13 +3827,13 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8904
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3835,19 +3845,19 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3864,13 +3874,14 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">81
+1198
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -3882,19 +3893,19 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3906,7 +3917,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -3918,7 +3929,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3930,7 +3941,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3941,19 +3952,19 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3971,13 +3982,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3260
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3995,7 +4006,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -4014,44 +4025,49 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4063,13 +4079,13 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4087,19 +4103,19 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4117,31 +4133,31 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2818
+          <t xml:space="preserve">2898
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -4153,19 +4169,20 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">9799791979277
+2 8
 </t>
         </is>
       </c>
@@ -4177,13 +4194,13 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4195,13 +4212,13 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2108
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -4213,13 +4230,13 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1768
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4243,19 +4260,19 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8308
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4273,13 +4290,13 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23059
+          <t xml:space="preserve">1999
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11219
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4291,7 +4308,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4309,74 +4326,69 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>7144</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1821
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -4392,16 +4404,10 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
+      <c r="X29" s="2" t="n"/>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -4424,7 +4430,8 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
+          <t xml:space="preserve">1921
+188181
 </t>
         </is>
       </c>
@@ -4433,62 +4440,53 @@
           <t>7162</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686
+</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">9661
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>45700</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">666
-</t>
+          <t>66611</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115656
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>3501</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7197
+</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10562
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -4497,25 +4495,48 @@
           <t>8244</t>
         </is>
       </c>
-      <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="n"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368883
+101
+</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9242175
+993 6
+</t>
+        </is>
+      </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="n"/>
-      <c r="W30" s="2" t="n"/>
-      <c r="X30" s="2" t="n"/>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
+          <t>2461</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+1
+17
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="n"/>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>751</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4532,13 +4553,13 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4578,11 +4599,10 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4593,13 +4613,12 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11705
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4611,7 +4630,7 @@
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4621,18 +4640,8 @@
 </t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">69
@@ -4641,31 +4650,27 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="n"/>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4682,13 +4687,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -4700,64 +4705,60 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4769,20 +4770,14 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7900
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="n"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4797,16 +4792,17 @@
 </t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+710
+</t>
+        </is>
+      </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -4824,13 +4820,13 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2355
+          <t xml:space="preserve">4828
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4842,25 +4838,25 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8786
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4870,15 +4866,10 @@
 </t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1157
-</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4890,25 +4881,25 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -4920,7 +4911,7 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4930,15 +4921,10 @@
 </t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11144
-</t>
-        </is>
-      </c>
+      <c r="U33" s="2" t="n"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -4950,19 +4936,19 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4986,13 +4972,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">4241
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -5003,13 +4990,14 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">112179 1
+</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -5026,7 +5014,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5038,61 +5026,62 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7144
+</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5104,13 +5093,14 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">14
+247
 </t>
         </is>
       </c>
@@ -5134,36 +5124,36 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4928
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112150
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>436</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1937
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5181,7 +5171,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -5193,19 +5183,20 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">14181
+60
 </t>
         </is>
       </c>
@@ -5217,7 +5208,7 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">1457
 </t>
         </is>
       </c>
@@ -5229,13 +5220,13 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6009
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -5247,28 +5238,23 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">12067
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">758
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1851
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="n"/>
       <c r="Z35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">60
@@ -5295,25 +5281,25 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1539
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -5325,13 +5311,13 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2235
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5349,19 +5335,14 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">9180
 </t>
         </is>
       </c>
@@ -5373,7 +5354,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
@@ -5385,19 +5366,19 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5415,7 +5396,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1661
 </t>
         </is>
       </c>
@@ -5427,7 +5408,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5445,24 +5426,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">658
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -5473,47 +5452,38 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">6139
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757
-</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t xml:space="preserve">757
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1490
+          <t xml:space="preserve">44980
 </t>
         </is>
       </c>
@@ -5525,54 +5495,57 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t xml:space="preserve">581
+</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8098
+          <t xml:space="preserve">8048
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
-        </is>
-      </c>
-      <c r="Y37" s="2" t="inlineStr"/>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5590,7 +5563,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5608,25 +5581,25 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5636,72 +5609,66 @@
 </t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
+</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61718682
+68
+8987
+</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 8
+21 0
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+14
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">314
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="n"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -5716,7 +5683,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1731
+          <t xml:space="preserve">1721
 </t>
         </is>
       </c>
@@ -5746,19 +5713,19 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3955
+          <t xml:space="preserve">583
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5769,7 +5736,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -5780,13 +5747,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -5798,18 +5764,19 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>466</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>50</t>
         </is>
       </c>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">10
+8917
 </t>
         </is>
       </c>
@@ -5820,42 +5787,43 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1536
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">647
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11911
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -5867,13 +5835,13 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">714
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5890,12 +5858,13 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>54521</t>
+          <t xml:space="preserve">5451
+</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -5919,25 +5888,25 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">23530
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5949,14 +5918,20 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n"/>
+          <t xml:space="preserve">13536
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1
+6
 </t>
         </is>
       </c>
@@ -5968,7 +5943,7 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -5980,7 +5955,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5992,7 +5967,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -6004,19 +5979,19 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -6058,31 +6033,31 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6100,19 +6075,14 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1389
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">87701
 </t>
         </is>
       </c>
@@ -6124,19 +6094,19 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">2382
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6154,13 +6124,13 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">16585
 </t>
         </is>
       </c>
@@ -6202,31 +6172,27 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">191
+181
+</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6238,38 +6204,44 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6146
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16211
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n"/>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2924
+991
+</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 111
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6281,7 +6253,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -6293,43 +6265,43 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1898
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
@@ -6347,144 +6319,140 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53109
+          <t xml:space="preserve">570
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18070
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2008
+</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3170
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9271
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="W43" s="2" t="n"/>
+      <c r="X43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1184
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1910
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -6502,145 +6470,143 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8571
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">634
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">610
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5409
+</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+1272971
+</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595
+</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1836
-</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1896
-</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5408
-</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1595
-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">4668
 </t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7240
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6658,84 +6624,76 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
+          <t xml:space="preserve">2830
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">708
+</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2152
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">11
 </t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6210
-</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">708
-</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8985
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8511
+          <t xml:space="preserve">8871
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5409
-</t>
-        </is>
-      </c>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -6746,38 +6704,44 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9756
+          <t xml:space="preserve">9792
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35611
+          <t xml:space="preserve">3511
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">92926
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="Z45" s="2" t="n"/>
@@ -6801,25 +6765,21 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+4236
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -6844,25 +6804,19 @@
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6880,7 +6834,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6892,25 +6846,20 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="n"/>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6920,12 +6869,7 @@
 </t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
+      <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6939,12 +6883,6 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1
@@ -6957,34 +6895,40 @@
 </t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">11984
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">4
+27
+78
+1
+646 7
 </t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t xml:space="preserve">114146
-</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>69</t>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+1
+1
+</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5823
+          <t xml:space="preserve">5829
 </t>
         </is>
       </c>
@@ -642,7 +642,12 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -651,25 +656,54 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n"/>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -684,13 +718,32 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n"/>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1520
+</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11207
+</t>
+        </is>
+      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -711,27 +764,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
-</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
+          <t xml:space="preserve">2889
+</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
@@ -743,26 +806,61 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
@@ -786,7 +884,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -796,7 +894,12 @@
 </t>
         </is>
       </c>
-      <c r="Y5" s="2" t="n"/>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755
+</t>
+        </is>
+      </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">60
@@ -817,45 +920,106 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25089
-</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
+          <t xml:space="preserve">5089
+</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">1180
+</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
         </is>
       </c>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2" t="n"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">619
@@ -870,24 +1034,34 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="n"/>
-      <c r="Z6" s="2" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>3</t>
@@ -906,7 +1080,12 @@
 </t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">132
@@ -915,48 +1094,80 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11898
+</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1236
+</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">5930
+</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="n"/>
-      <c r="R7" s="2" t="n"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -968,20 +1179,40 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11918
-</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="n"/>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="n"/>
-      <c r="Y7" s="2" t="n"/>
-      <c r="Z7" s="2" t="n"/>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1000,10 +1231,15 @@
 </t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">419
+</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1019,7 +1255,12 @@
 </t>
         </is>
       </c>
-      <c r="H8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">18
@@ -1034,7 +1275,8 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">272
+</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1049,26 +1291,51 @@
 </t>
         </is>
       </c>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1078,7 +1345,12 @@
 </t>
         </is>
       </c>
-      <c r="W8" s="2" t="n"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="n"/>
       <c r="Y8" s="2" t="n"/>
       <c r="Z8" s="2" t="n"/>
@@ -1108,7 +1380,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
@@ -1120,37 +1392,55 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t xml:space="preserve">8815
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">651
+</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="n"/>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">607
+</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t xml:space="preserve">860
+</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4590
+          <t xml:space="preserve">9590
 </t>
         </is>
       </c>
@@ -1162,29 +1452,55 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11140
+          <t xml:space="preserve">11940
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="n"/>
-      <c r="T9" s="2" t="n"/>
-      <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="n"/>
-      <c r="W9" s="2" t="n"/>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">068
+</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21626
+</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9590
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0098
+</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">4198
 </t>
         </is>
       </c>
@@ -1201,56 +1517,137 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4490
+</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="n"/>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">629
+</t>
+        </is>
+      </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8908
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4150
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1268,117 +1665,117 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94450
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n"/>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="n"/>
+          <t xml:space="preserve">2104
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="n"/>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1188
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1394,95 +1791,142 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2918
-</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
+          <t xml:space="preserve">2290
+</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n"/>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n"/>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
+          <t xml:space="preserve">1835
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">745
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="n"/>
-      <c r="X12" s="2" t="n"/>
-      <c r="Y12" s="2" t="n"/>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2408
+</t>
+        </is>
+      </c>
       <c r="Z12" s="2" t="n"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1496,90 +1940,143 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3220
+</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="n"/>
+          <t xml:space="preserve">905
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="n"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -1592,15 +2089,40 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3240
+</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
@@ -1610,47 +2132,97 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="2" t="n"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="n"/>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="n"/>
+          <t xml:space="preserve">719
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="n"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="n"/>
+          <t xml:space="preserve">875
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>9</t>
@@ -1663,70 +2235,138 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3079
+</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n"/>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">968
+</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="n"/>
-      <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="n"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="inlineStr"/>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="n"/>
-      <c r="Y15" s="2" t="n"/>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="n"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -1739,75 +2379,148 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19722
+</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911
+</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6494
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
+          <t xml:space="preserve">468
+</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912
+</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">648
+</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">969
 </t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">838
+</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">884
+</t>
+        </is>
+      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="n"/>
+          <t xml:space="preserve">1648
+</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="n"/>
+          <t xml:space="preserve">1806
+</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">851
+</t>
+        </is>
+      </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="n"/>
+          <t xml:space="preserve">4888
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1822,133 +2535,139 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19722
+          <t xml:space="preserve">2250
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11148
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1674
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4214
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1164646</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0962
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0828
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8880
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17186
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24208
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1966,96 +2685,138 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
+          <t xml:space="preserve">4288
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n"/>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t xml:space="preserve">140
+</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n"/>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="n"/>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="n"/>
-      <c r="Y18" s="2" t="n"/>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="n"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2070,79 +2831,125 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4285
+          <t xml:space="preserve">8406
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1109
-</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="n"/>
-      <c r="S19" s="2" t="n"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">540
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="n"/>
-      <c r="W19" s="2" t="n"/>
-      <c r="X19" s="2" t="n"/>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">810
@@ -2151,7 +2958,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -2169,73 +2976,138 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24406
+          <t xml:space="preserve">1531
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">920
 </t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="n"/>
-      <c r="S20" s="2" t="n"/>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">599
-</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="n"/>
-      <c r="W20" s="2" t="n"/>
-      <c r="X20" s="2" t="n"/>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="n"/>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>13</t>
@@ -2250,68 +3122,148 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
+          <t xml:space="preserve">1419
+</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2119
+</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="n"/>
-      <c r="S21" s="2" t="n"/>
+          <t xml:space="preserve">908
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1215
+</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="n"/>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 8
+</t>
+        </is>
+      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="n"/>
-      <c r="X21" s="2" t="n"/>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="n"/>
+          <t xml:space="preserve">8809
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -2326,85 +3278,145 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12617
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+          <t xml:space="preserve">11206
+</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1944
+</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n"/>
+          <t xml:space="preserve">4134
+</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n"/>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="n"/>
-      <c r="W22" s="2" t="n"/>
-      <c r="X22" s="2" t="n"/>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8709
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2422,100 +3434,144 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">19212
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n"/>
+          <t xml:space="preserve">111531
+</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">494
+</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n"/>
+          <t xml:space="preserve">9408
+</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">431
+</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
+          <t xml:space="preserve">382
+</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1221
+</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">8164
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>649</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="n"/>
+          <t xml:space="preserve">1090
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">3479
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="n"/>
-      <c r="X23" s="2" t="n"/>
+          <t xml:space="preserve">406
+</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9189
+</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">899
+</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9118
+</t>
+        </is>
+      </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -2533,133 +3589,135 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19832
+          <t xml:space="preserve">2154
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9437
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6444</t>
-        </is>
-      </c>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">695
+</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">28
 </t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>3321</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171621
-</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804618
-</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1090
-</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
-</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3479
-</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>4064</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2676,97 +3734,143 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354
+          <t xml:space="preserve">4904
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n"/>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">2128
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n"/>
+          <t xml:space="preserve">18492
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n"/>
+          <t xml:space="preserve">9108
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">2019
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">689
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="T25" s="2" t="n"/>
-      <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="n"/>
-      <c r="X25" s="2" t="n"/>
-      <c r="Y25" s="2" t="n"/>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="n"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -2781,88 +3885,143 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4904
+          <t xml:space="preserve">2878
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n"/>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n"/>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1 5
 </t>
         </is>
       </c>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1846
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="n"/>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr"/>
-      <c r="U26" s="2" t="n"/>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">730
+</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="n"/>
-      <c r="Y26" s="2" t="n"/>
-      <c r="Z26" s="2" t="n"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -2875,79 +4034,150 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23059
+</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n"/>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="n"/>
-      <c r="R27" s="2" t="n"/>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1730
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="n"/>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="n"/>
-      <c r="X27" s="2" t="n"/>
-      <c r="Y27" s="2" t="n"/>
-      <c r="Z27" s="2" t="n"/>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -2960,80 +4190,148 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20239
+</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+          <t xml:space="preserve">11179
+</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
+          <t xml:space="preserve">1654
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="n"/>
-      <c r="R28" s="2" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="n"/>
-      <c r="V28" s="2" t="n"/>
-      <c r="W28" s="2" t="n"/>
-      <c r="X28" s="2" t="n"/>
-      <c r="Y28" s="2" t="n"/>
-      <c r="Z28" s="2" t="n"/>
+          <t xml:space="preserve">728
+</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">838
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -3048,73 +4346,143 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3059
+          <t xml:space="preserve">2898
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
+          <t xml:space="preserve">1219
+</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n"/>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n"/>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1950
-</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n"/>
-      <c r="Q29" s="2" t="n"/>
-      <c r="R29" s="2" t="n"/>
-      <c r="S29" s="2" t="n"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="n"/>
-      <c r="V29" s="2" t="n"/>
-      <c r="W29" s="2" t="n"/>
-      <c r="X29" s="2" t="n"/>
-      <c r="Y29" s="2" t="n"/>
-      <c r="Z29" s="2" t="n"/>
+          <t xml:space="preserve">700
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>20</t>
@@ -3129,83 +4497,146 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
+          <t xml:space="preserve">16829
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
+          <t xml:space="preserve">11209
+</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">006
+</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">437
+</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">656
+</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>4566</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200214
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5619
+</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3946
+</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="n"/>
-      <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="n"/>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1822009
-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="n"/>
-      <c r="Z30" s="2" t="n"/>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4418
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3220,125 +4651,145 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16099
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t xml:space="preserve">137
+</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>420344</t>
+          <t xml:space="preserve">941
+</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1054
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3611
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94910
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3355,97 +4806,138 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
+          <t xml:space="preserve">4828
+</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">88
 </t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="n"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8950
+</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">110
 </t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="n"/>
-      <c r="T32" s="2" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9011
+</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2810
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="n"/>
-      <c r="Y32" s="2" t="n"/>
-      <c r="Z32" s="2" t="n"/>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -3458,96 +4950,140 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4828
+</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1897
+</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="n"/>
-      <c r="W33" s="2" t="n"/>
-      <c r="X33" s="2" t="n"/>
+          <t xml:space="preserve">1144
+</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1834
+</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1406
+</t>
+        </is>
+      </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -3563,67 +5099,147 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4928
+</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1250
+</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11136
+</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n"/>
+          <t xml:space="preserve">1083
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
-</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n"/>
-      <c r="Q34" s="2" t="n"/>
-      <c r="R34" s="2" t="n"/>
-      <c r="S34" s="2" t="n"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="n"/>
-      <c r="W34" s="2" t="n"/>
-      <c r="X34" s="2" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1167
+</t>
+        </is>
+      </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
@@ -3639,67 +5255,145 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740
+</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">2894
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1135
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="n"/>
-      <c r="Q35" s="2" t="n"/>
-      <c r="R35" s="2" t="n"/>
-      <c r="S35" s="2" t="n"/>
+          <t xml:space="preserve">91800
+</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="n"/>
-      <c r="V35" s="2" t="n"/>
-      <c r="W35" s="2" t="n"/>
-      <c r="X35" s="2" t="n"/>
-      <c r="Y35" s="2" t="n"/>
+          <t xml:space="preserve">6008
+</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114248
+</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755
+</t>
+        </is>
+      </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -3715,12 +5409,27 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4983
+</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -3730,8 +5439,17 @@
 </t>
         </is>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -3740,31 +5458,61 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="Q36" s="2" t="n"/>
-      <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="n"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11242
+</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1710
+</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">5521
 </t>
         </is>
       </c>
@@ -3775,9 +5523,24 @@
 </t>
         </is>
       </c>
-      <c r="W36" s="2" t="n"/>
-      <c r="X36" s="2" t="n"/>
-      <c r="Y36" s="2" t="n"/>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798
+</t>
+        </is>
+      </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">45
@@ -3798,106 +5561,139 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11828
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8258
+</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">040
+</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">291
+</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n"/>
+          <t xml:space="preserve">80120
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94490
+          <t xml:space="preserve">4490
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">3134
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12910
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t xml:space="preserve">809
+</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9092
+          <t xml:space="preserve">9402
 </t>
         </is>
       </c>
@@ -3925,17 +5721,32 @@
 </t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3947,14 +5758,15 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t xml:space="preserve">1151
+</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -3963,10 +5775,15 @@
 </t>
         </is>
       </c>
-      <c r="N38" s="2" t="n"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1521
+</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -3976,16 +5793,36 @@
 </t>
         </is>
       </c>
-      <c r="Q38" s="2" t="n"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="n"/>
-      <c r="T38" s="2" t="n"/>
-      <c r="U38" s="2" t="n"/>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">182
@@ -3994,12 +5831,28 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="n"/>
-      <c r="Y38" s="2" t="n"/>
-      <c r="Z38" s="2" t="n"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2249
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 0
+</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4014,93 +5867,138 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13953
+          <t xml:space="preserve">3950
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1115
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1187
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">528
+</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1710
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="Q39" s="2" t="n"/>
-      <c r="R39" s="2" t="n"/>
-      <c r="S39" s="2" t="n"/>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5208
-</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="n"/>
-      <c r="X39" s="2" t="n"/>
-      <c r="Y39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">718
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="2" t="n"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -4115,64 +6013,140 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>40344</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
+          <t xml:space="preserve">29421
+</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2188
+</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1115
+</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">0016
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
-      <c r="N40" s="2" t="n"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="n"/>
-      <c r="Q40" s="2" t="n"/>
-      <c r="R40" s="2" t="n"/>
-      <c r="S40" s="2" t="n"/>
-      <c r="T40" s="2" t="n"/>
+          <t xml:space="preserve">2995
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">685
+</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="n"/>
-      <c r="X40" s="2" t="n"/>
-      <c r="Y40" s="2" t="n"/>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
+</t>
+        </is>
+      </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4190,44 +6164,74 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
-</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
+          <t xml:space="preserve">4084
+</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1125
+</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1111
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="n"/>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -4237,38 +6241,62 @@
 </t>
         </is>
       </c>
-      <c r="Q41" s="2" t="n"/>
-      <c r="R41" s="2" t="n"/>
-      <c r="S41" s="2" t="n"/>
-      <c r="T41" s="2" t="n"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11239
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1625
+</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X41" s="2" t="n"/>
+          <t xml:space="preserve">1720
+</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4286,64 +6314,130 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13370
-</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
+          <t xml:space="preserve">3491
+</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1224
+</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">889
+</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434
+</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14605
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">104
 </t>
         </is>
       </c>
-      <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="n"/>
-      <c r="R42" s="2" t="n"/>
-      <c r="S42" s="2" t="n"/>
-      <c r="T42" s="2" t="n"/>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>1424</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="n"/>
-      <c r="W42" s="2" t="n"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="X42" s="2" t="n"/>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">987
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4361,85 +6455,132 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16531
-</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
+          <t xml:space="preserve">5170
+</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101
+</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="n"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="n"/>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9593
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="n"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="W43" s="2" t="n"/>
-      <c r="X43" s="2" t="n"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -4457,21 +6598,41 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228301
+          <t xml:space="preserve">6531
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
-</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">50
@@ -4484,7 +6645,12 @@
 </t>
         </is>
       </c>
-      <c r="L44" s="2" t="n"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">126
@@ -4498,32 +6664,42 @@
 </t>
         </is>
       </c>
-      <c r="P44" s="2" t="n"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="Q44" s="2" t="n"/>
-      <c r="R44" s="2" t="n"/>
-      <c r="S44" s="2" t="n"/>
-      <c r="T44" s="2" t="n"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1681
+</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595
+</t>
+        </is>
+      </c>
       <c r="U44" s="2" t="n"/>
-      <c r="V44" s="2" t="n"/>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">958
-</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">996
-</t>
-        </is>
-      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
       <c r="Y44" s="2" t="n"/>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
+      <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -4536,70 +6712,149 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22830
+</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1985
+</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2191
+</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
+</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409
-</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="n"/>
-      <c r="R45" s="2" t="n"/>
+          <t xml:space="preserve">2909
+</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1216
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="n"/>
-      <c r="U45" s="2" t="n"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3810
+</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1690
+</t>
+        </is>
+      </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1118
 </t>
         </is>
       </c>
-      <c r="W45" s="2" t="n"/>
-      <c r="X45" s="2" t="n"/>
-      <c r="Y45" s="2" t="n"/>
-      <c r="Z45" s="2" t="n"/>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2208
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">896
+</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>46484</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4614,19 +6869,20 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294970
+          <t xml:space="preserve">4980
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4637,44 +6893,70 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1389
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2541
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">171
@@ -4687,22 +6969,48 @@
 </t>
         </is>
       </c>
-      <c r="T46" s="2" t="n"/>
-      <c r="U46" s="2" t="n"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">585
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="n"/>
-      <c r="Z46" s="2" t="n"/>
+          <t xml:space="preserve">1159
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
@@ -626,14 +626,13 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5829
+          <t xml:space="preserve">5822
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -662,17 +661,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">92
+</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -690,7 +691,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -726,24 +727,20 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1520
-</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11207
+          <t xml:space="preserve">10 7 1
 </t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -764,13 +761,13 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">3885
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">2291
 </t>
         </is>
       </c>
@@ -794,7 +791,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -806,14 +803,13 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -824,13 +820,13 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -842,7 +838,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -896,7 +892,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -938,7 +934,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -974,19 +970,19 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1309
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -1004,7 +1000,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -1040,13 +1036,13 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1058,7 +1054,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1086,15 +1082,10 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11898
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1106,25 +1097,25 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -1136,26 +1127,25 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1521
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5930
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1167,7 +1157,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1179,7 +1169,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1191,7 +1181,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -1203,13 +1193,13 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1233,7 +1223,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">419
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1275,8 +1265,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1293,13 +1282,13 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -1323,7 +1312,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1335,7 +1324,7 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
@@ -1380,7 +1369,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -1392,56 +1381,49 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8815
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
-</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">631
+</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">511
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">734
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">607
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590
-</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1452,7 +1434,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11940
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -1464,13 +1446,13 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">068
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21626
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
@@ -1482,13 +1464,13 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9590
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0098
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -1500,7 +1482,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198
+          <t xml:space="preserve">8481
 </t>
         </is>
       </c>
@@ -1519,7 +1501,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
+          <t xml:space="preserve">4950
 </t>
         </is>
       </c>
@@ -1537,7 +1519,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -1555,13 +1537,13 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1586,13 +1568,13 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">9218
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">11 3 8
 </t>
         </is>
       </c>
@@ -1605,13 +1587,13 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1782
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -1665,8 +1647,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218
-</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1677,97 +1658,86 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2104
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1815,7 +1785,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -1845,13 +1815,13 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1835
+          <t xml:space="preserve">1385
 </t>
         </is>
       </c>
@@ -1863,7 +1833,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1905,7 +1875,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1923,7 +1893,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2408
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1960,18 +1930,19 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -1995,7 +1966,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -2017,11 +1988,7 @@
 </t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
+      <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1158
@@ -2036,13 +2003,13 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -2061,13 +2028,13 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -2098,14 +2065,13 @@
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">0134
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2116,25 +2082,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
@@ -2152,8 +2117,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2170,8 +2134,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -2182,13 +2145,13 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
@@ -2200,7 +2163,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2250,12 +2213,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -2273,7 +2236,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">18 2
 </t>
         </is>
       </c>
@@ -2291,7 +2254,8 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2308,7 +2272,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -2381,7 +2345,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19722
+          <t xml:space="preserve">19732
 </t>
         </is>
       </c>
@@ -2393,33 +2357,28 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6494
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">644
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">69
@@ -2428,13 +2387,13 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
@@ -2446,43 +2405,39 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">069
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
-</t>
+          <t>39452</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2493,13 +2448,13 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2511,7 +2466,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4888
+          <t xml:space="preserve">4288
 </t>
         </is>
       </c>
@@ -2535,8 +2490,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2250
-</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2547,18 +2501,18 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -2576,7 +2530,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -2595,31 +2549,31 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -2631,13 +2585,13 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">789
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2691,13 +2645,13 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2709,8 +2663,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2721,7 +2674,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2733,80 +2686,84 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">691
-</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -2831,13 +2788,14 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8406
+          <t xml:space="preserve">4406
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2854,20 +2812,19 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2896,8 +2853,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2914,7 +2870,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2938,15 +2894,19 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="n"/>
-      <c r="W19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">11853
 </t>
         </is>
       </c>
@@ -2958,7 +2918,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
@@ -2982,7 +2942,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -2994,7 +2954,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3007,7 +2967,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3050,44 +3010,38 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">876
+</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">768
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">768
-</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -3140,31 +3094,31 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1419
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3176,7 +3130,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1562
 </t>
         </is>
       </c>
@@ -3188,8 +3142,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -3206,7 +3159,7 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -3218,8 +3171,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>0431</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -3230,13 +3182,13 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 8
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
@@ -3284,13 +3236,13 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11206
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3302,13 +3254,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -3318,12 +3270,7 @@
 </t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
+      <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -3332,7 +3279,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3344,13 +3291,13 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3380,7 +3327,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">7408
 </t>
         </is>
       </c>
@@ -3392,7 +3339,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -3416,7 +3363,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3434,38 +3381,35 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19212
-</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111531
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9408
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">431
-</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3476,7 +3420,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -3488,25 +3432,19 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1221
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1614
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8164
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3523,13 +3461,12 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -3547,32 +3484,30 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9189
+          <t xml:space="preserve">9198
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9118
-</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">484
+          <t xml:space="preserve">1488
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3633,8 +3568,7 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>459</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3645,7 +3579,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3680,7 +3614,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">695
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
@@ -3698,13 +3632,13 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3734,25 +3668,24 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4904
+          <t xml:space="preserve">1304
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>46431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3764,7 +3697,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3776,32 +3709,31 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18492
+          <t xml:space="preserve">1342
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3818,25 +3750,25 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1729
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
@@ -3848,22 +3780,16 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">940
@@ -3885,7 +3811,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2878
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
@@ -3915,26 +3841,21 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 5
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -3956,15 +3877,10 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+      <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -3994,32 +3910,30 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4036,7 +3950,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23059
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
@@ -4048,115 +3962,113 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1154
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1190
-</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4192,7 +4104,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20239
+          <t xml:space="preserve">3059
 </t>
         </is>
       </c>
@@ -4210,8 +4122,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11179
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4222,34 +4133,29 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">142
@@ -4258,7 +4164,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -4269,7 +4175,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4299,7 +4205,7 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -4352,7 +4258,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4364,14 +4270,13 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -4389,25 +4294,25 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4419,8 +4324,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4443,7 +4347,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
@@ -4497,19 +4401,19 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16829
+          <t xml:space="preserve">16899
 </t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">11298
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
@@ -4533,7 +4437,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4545,7 +4449,8 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t xml:space="preserve">386
+</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4556,36 +4461,31 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200214
+          <t xml:space="preserve">4798
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4597,7 +4497,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5619
+          <t xml:space="preserve">5618
 </t>
         </is>
       </c>
@@ -4607,33 +4507,28 @@
 </t>
         </is>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">880
 </t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4418
+          <t xml:space="preserve">4 16 8
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4657,7 +4552,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4681,7 +4576,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -4693,16 +4588,11 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1 8
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">149
@@ -4711,13 +4601,13 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -4753,13 +4643,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4783,13 +4672,13 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4806,7 +4695,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4818
 </t>
         </is>
       </c>
@@ -4818,19 +4707,19 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1719
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -4840,58 +4729,52 @@
 </t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8950
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -4903,7 +4786,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9011
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
@@ -4915,13 +4798,13 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -4952,43 +4835,43 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
+          <t xml:space="preserve">4228
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2491
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">66184 5
+</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">1917
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4998,11 +4881,7 @@
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">130
@@ -5011,7 +4890,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1924
 </t>
         </is>
       </c>
@@ -5021,12 +4900,7 @@
 </t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+      <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -5041,19 +4915,19 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">3195
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -5065,19 +4939,19 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -5107,19 +4981,18 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5131,25 +5004,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1083
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5161,13 +5033,13 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1916
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -5179,7 +5051,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5191,7 +5063,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5203,7 +5075,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -5221,16 +5093,11 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr"/>
       <c r="Y34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">210
@@ -5239,7 +5106,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -5257,13 +5124,13 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">2180
 </t>
         </is>
       </c>
@@ -5275,8 +5142,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -5304,7 +5170,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5316,72 +5182,73 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">17
 </t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91800
-</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2188
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6008
-</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114248
-</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5429,24 +5296,20 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5476,7 +5339,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -5494,7 +5357,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -5506,13 +5369,13 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5521
+          <t xml:space="preserve">551
 </t>
         </is>
       </c>
@@ -5561,86 +5424,79 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8258
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">040
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80120
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">831
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
-</t>
+          <t>449303</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5651,13 +5507,13 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5669,13 +5525,13 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -5687,22 +5543,16 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9402
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1281
-</t>
-        </is>
-      </c>
+          <t>412524</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5717,7 +5567,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94386
+          <t xml:space="preserve">4386
 </t>
         </is>
       </c>
@@ -5741,31 +5591,36 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -5777,19 +5632,18 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">1581
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5807,14 +5661,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
-</t>
+          <t>639</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -5831,7 +5683,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -5843,13 +5695,13 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 0
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5867,19 +5719,19 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3950
+          <t xml:space="preserve">23923
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
@@ -5891,17 +5743,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">52
@@ -5910,23 +5762,28 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5015
+</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">910
@@ -5941,7 +5798,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
@@ -5953,31 +5810,31 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1710
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5989,13 +5846,13 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6019,119 +5876,103 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">2492
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0016
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588
+</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">194
 </t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2995
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">685
-</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
+      <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -6176,7 +6017,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -6188,7 +6029,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6200,7 +6041,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">9810
 </t>
         </is>
       </c>
@@ -6224,14 +6065,14 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6243,13 +6084,13 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11239
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -6261,24 +6102,25 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>09</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6296,7 +6138,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6314,19 +6156,19 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
+          <t xml:space="preserve">3401
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -6339,11 +6181,16 @@
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40
@@ -6358,13 +6205,13 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -6388,13 +6235,13 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">434
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -6406,7 +6253,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
@@ -6455,13 +6302,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5170
+          <t xml:space="preserve">5370
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>495</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -6473,32 +6320,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">1 18
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -6509,18 +6355,19 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -6536,12 +6383,7 @@
 </t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1165
-</t>
-        </is>
-      </c>
+      <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">156
@@ -6550,13 +6392,13 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -6598,7 +6440,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6531
+          <t xml:space="preserve">2231
 </t>
         </is>
       </c>
@@ -6647,8 +6489,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -6666,14 +6507,14 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q44" s="2" t="n"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1681
+          <t xml:space="preserve">1671
 </t>
         </is>
       </c>
@@ -6692,7 +6533,7 @@
       <c r="U44" s="2" t="n"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
@@ -6714,144 +6555,144 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22830
+          <t xml:space="preserve">22820
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">19818
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">2862
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1801
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2909
+          <t xml:space="preserve">2409
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3810
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t xml:space="preserve">9668
+</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6869,7 +6710,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4980
+          <t xml:space="preserve">4970
 </t>
         </is>
       </c>
@@ -6881,7 +6722,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -6915,12 +6756,7 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
+      <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">149
@@ -6929,25 +6765,25 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1389
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2541
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6975,12 +6811,7 @@
 </t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-</t>
-        </is>
-      </c>
+      <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -6989,19 +6820,19 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
@@ -626,13 +626,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5822
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -667,19 +668,19 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -691,7 +692,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">1295
 </t>
         </is>
       </c>
@@ -727,23 +728,23 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 7 1
-</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9187
+</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="n"/>
       <c r="Z4" s="2" t="n"/>
@@ -761,13 +762,13 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3885
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2291
+          <t xml:space="preserve">2939
 </t>
         </is>
       </c>
@@ -791,54 +792,55 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1535
+</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -850,13 +852,13 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -868,7 +870,7 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -892,7 +894,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">755
 </t>
         </is>
       </c>
@@ -916,7 +918,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
@@ -928,26 +930,25 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">2128
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -964,7 +965,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -976,19 +977,19 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1018,7 +1019,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -1042,20 +1043,19 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1082,10 +1082,15 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -1097,13 +1102,13 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1115,7 +1120,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -1133,31 +1138,37 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -1175,13 +1186,13 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -1193,13 +1204,13 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1223,7 +1234,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -1253,96 +1264,111 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="X8" s="2" t="n"/>
-      <c r="Y8" s="2" t="n"/>
-      <c r="Z8" s="2" t="n"/>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1357,19 +1383,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22249
+          <t xml:space="preserve">2224
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">11185
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
@@ -1381,7 +1407,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -1391,10 +1417,14 @@
 </t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7064</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1411,19 +1441,20 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t xml:space="preserve">590
+</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1446,7 +1477,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -1458,35 +1489,35 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1151
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">940
 </t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">897
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8481
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="n"/>
+      <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1501,7 +1532,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
+          <t xml:space="preserve">445
 </t>
         </is>
       </c>
@@ -1519,7 +1550,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1537,17 +1568,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">97 9
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">147
@@ -1568,17 +1599,22 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 3 8
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">176
@@ -1587,13 +1623,13 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1782
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1605,7 +1641,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -1623,13 +1659,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1647,12 +1683,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -1664,18 +1700,27 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">07
@@ -1684,48 +1729,48 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1737,16 +1782,45 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="n"/>
-      <c r="X11" s="2" t="n"/>
-      <c r="Y11" s="2" t="n"/>
-      <c r="Z11" s="2" t="n"/>
+          <t xml:space="preserve">1406491
+</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">341
+</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6817
+</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57175
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">804940
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1761,7 +1835,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">2295
 </t>
         </is>
       </c>
@@ -1773,7 +1847,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1785,7 +1859,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -1815,25 +1889,25 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1385
+          <t xml:space="preserve">1839
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">9318
 </t>
         </is>
       </c>
@@ -1857,47 +1931,40 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
-</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="n"/>
+          <t>9405</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>7</t>
@@ -1942,7 +2009,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1966,7 +2033,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -1978,63 +2045,73 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">925
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
+</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">945
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
@@ -2062,16 +2139,22 @@
 </t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0134
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2082,12 +2165,13 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2099,7 +2183,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -2117,12 +2201,13 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
@@ -2134,7 +2219,8 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">217
+</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -2145,38 +2231,43 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">719
+</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">715
-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">875
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -2204,7 +2295,12 @@
 </t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">132
@@ -2213,7 +2309,8 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2224,31 +2321,31 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 2
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2266,13 +2363,13 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">0911
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2302,35 +2399,40 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">62
 </t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">157
 </t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="n"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>10</t>
@@ -2345,7 +2447,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19732
+          <t xml:space="preserve">1475
 </t>
         </is>
       </c>
@@ -2357,37 +2459,41 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1644
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -2399,62 +2505,64 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t xml:space="preserve">11404
+</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">069
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t xml:space="preserve">830
+</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39452</t>
+          <t xml:space="preserve">3945
+</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
@@ -2466,13 +2574,13 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4288
+          <t xml:space="preserve">12088
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2490,29 +2598,31 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t xml:space="preserve">2950
+</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">088
+</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -2530,11 +2640,16 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">28 14
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2695
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">146
@@ -2543,70 +2658,70 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">929
 </t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">789
-</t>
-        </is>
-      </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">50
 </t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">172
@@ -2615,14 +2730,13 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2639,7 +2753,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4288
+          <t xml:space="preserve">4283
 </t>
         </is>
       </c>
@@ -2651,129 +2765,125 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1701
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="Z18" s="2" t="n"/>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>11</t>
@@ -2794,7 +2904,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -2812,7 +2922,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">5140
 </t>
         </is>
       </c>
@@ -2824,7 +2934,8 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2841,7 +2952,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
@@ -2853,7 +2964,8 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2864,13 +2976,13 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2149
 </t>
         </is>
       </c>
@@ -2898,15 +3010,21 @@
 </t>
         </is>
       </c>
-      <c r="V19" s="2" t="n"/>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">1870
+</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11853
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2918,7 +3036,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2942,23 +3060,28 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -2967,11 +3090,15 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">56
@@ -2980,19 +3107,18 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>454</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3004,19 +3130,19 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -3032,16 +3158,22 @@
 </t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -3082,7 +3214,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3100,13 +3232,13 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -3130,7 +3262,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1562
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3142,12 +3274,13 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t xml:space="preserve">117
+</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
@@ -3159,7 +3292,7 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -3171,7 +3304,8 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0431</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -3188,7 +3322,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3200,13 +3334,13 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8809
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -3242,7 +3376,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3254,13 +3388,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -3270,7 +3404,12 @@
 </t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -3279,25 +3418,25 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
@@ -3321,13 +3460,13 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7408
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -3339,7 +3478,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -3357,13 +3496,12 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
-</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -3381,7 +3519,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3392,32 +3530,29 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t xml:space="preserve">943
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">99
@@ -3426,30 +3561,35 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1614
-</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>304</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -3461,7 +3601,8 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t xml:space="preserve">888
+</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -3484,30 +3625,30 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9198
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
+          <t xml:space="preserve">9295
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3542,103 +3683,115 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10434
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2211
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1183
 </t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3668,7 +3821,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3680,37 +3833,34 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46431</t>
+          <t xml:space="preserve">131
+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3721,66 +3871,61 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">1842
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">915
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1729
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3789,14 +3934,23 @@
 </t>
         </is>
       </c>
-      <c r="X25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">940
 </t>
         </is>
       </c>
-      <c r="Z25" s="2" t="n"/>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3811,25 +3965,25 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3845,23 +3999,33 @@
 </t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">15
 </t>
         </is>
       </c>
-      <c r="K26" s="2" t="n"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1846
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3877,7 +4041,12 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -3886,7 +4055,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
@@ -3922,18 +4091,20 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">885
+</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3950,25 +4121,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">059
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3979,60 +4151,56 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
+</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2108
 </t>
         </is>
       </c>
@@ -4050,13 +4218,13 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">7170
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4068,7 +4236,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4104,13 +4272,13 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3059
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4122,7 +4290,8 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4133,38 +4302,44 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1154
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1142
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -4181,7 +4356,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -4193,8 +4368,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -4205,7 +4379,8 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -4234,7 +4409,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -4270,108 +4445,115 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">171
 </t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">709
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
@@ -4401,7 +4583,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16899
+          <t xml:space="preserve">16099
 </t>
         </is>
       </c>
@@ -4411,12 +4593,7 @@
 </t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">606
-</t>
-        </is>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">906
@@ -4425,13 +4602,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
@@ -4443,7 +4619,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -4453,39 +4629,38 @@
 </t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">117
 </t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4798
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t xml:space="preserve">1052
+</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -4497,17 +4672,22 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618
+          <t xml:space="preserve">5610
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3946
-</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">345
+</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">811
@@ -4516,13 +4696,13 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 16 8
+          <t xml:space="preserve">4410
 </t>
         </is>
       </c>
@@ -4552,7 +4732,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -4576,7 +4756,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -4588,97 +4768,94 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">941
-</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">2144
+</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4695,56 +4872,55 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4818
-</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4753,7 +4929,12 @@
           <t>1051</t>
         </is>
       </c>
-      <c r="N32" s="2" t="n"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">830
@@ -4774,50 +4955,55 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">901
-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="n"/>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -4835,43 +5021,44 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4228
+          <t xml:space="preserve">14828
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66184 5
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1917
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1826
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4880,8 +5067,18 @@
 </t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">130
@@ -4890,7 +5087,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1924
+          <t xml:space="preserve">1848
 </t>
         </is>
       </c>
@@ -4900,7 +5097,12 @@
 </t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -4921,7 +5123,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3195
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -4933,19 +5135,19 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
@@ -4975,48 +5177,49 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4928
+          <t xml:space="preserve">4828
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">11095
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -5033,13 +5236,13 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -5063,7 +5266,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -5093,23 +5296,23 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
+      <c r="Z34" s="2" t="n"/>
       <c r="AA34" t="inlineStr">
         <is>
           <t>23</t>
@@ -5124,13 +5327,13 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">94928
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5142,24 +5345,24 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2894
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>72793</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -5182,19 +5385,19 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">9100
 </t>
         </is>
       </c>
@@ -5206,7 +5409,7 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2945
 </t>
         </is>
       </c>
@@ -5224,13 +5427,13 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">6008
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5242,19 +5445,19 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
@@ -5278,38 +5481,43 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4983
+          <t xml:space="preserve">94989
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">2942
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">14103
+</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5327,7 +5535,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
@@ -5339,7 +5547,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -5357,7 +5565,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1881
 </t>
         </is>
       </c>
@@ -5369,17 +5577,22 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
-</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="n"/>
+          <t xml:space="preserve">521
+</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">184
@@ -5394,7 +5607,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">1666
 </t>
         </is>
       </c>
@@ -5406,7 +5619,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5424,79 +5637,78 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">21928
 </t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1191
+</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>6657</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">533
+</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1106
+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">698
-</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">757
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7112
+</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>449303</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">88
+</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5513,7 +5725,7 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5525,7 +5737,7 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2348
 </t>
         </is>
       </c>
@@ -5537,22 +5749,27 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>412524</t>
-        </is>
-      </c>
-      <c r="Z37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">4098
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5567,7 +5784,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4386
+          <t xml:space="preserve">438
 </t>
         </is>
       </c>
@@ -5579,7 +5796,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -5591,18 +5808,19 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5612,16 +5830,10 @@
 </t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -5632,13 +5844,14 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1581
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5661,12 +5874,14 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t xml:space="preserve">827
+</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -5683,7 +5898,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -5695,13 +5910,13 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -5719,19 +5934,19 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23923
+          <t xml:space="preserve">395953
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -5743,7 +5958,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -5753,52 +5968,51 @@
 </t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8115
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
 </t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5015
-</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -5810,7 +6024,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
@@ -5822,38 +6036,30 @@
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">0158
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5870,47 +6076,55 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29421
-</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2492
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">191
+</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">160
@@ -5919,20 +6133,25 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5950,7 +6169,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -5972,22 +6191,27 @@
 </t>
         </is>
       </c>
-      <c r="W40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">4084
 </t>
         </is>
       </c>
@@ -6005,49 +6229,49 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4084
+          <t xml:space="preserve">3401
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1237
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9810
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6065,14 +6289,19 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
@@ -6084,31 +6313,31 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -6120,25 +6349,25 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -6156,74 +6385,79 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6235,13 +6469,13 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -6265,26 +6499,31 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="n"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -6302,78 +6541,85 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5370
+          <t xml:space="preserve">5571
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 18
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>07</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1354
 </t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6383,46 +6629,52 @@
 </t>
         </is>
       </c>
-      <c r="R43" s="2" t="n"/>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t xml:space="preserve">1867
+</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="n"/>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6440,107 +6692,148 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231
+          <t xml:space="preserve">29830
 </t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1417
 </t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1911
+</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1836
+</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="n"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="n"/>
+          <t xml:space="preserve">53409
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
+          <t xml:space="preserve">1024
 </t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="n"/>
+          <t xml:space="preserve">3510
+</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690
+</t>
+        </is>
+      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="n"/>
-      <c r="X44" s="2" t="n"/>
-      <c r="Y44" s="2" t="n"/>
-      <c r="Z44" s="2" t="n"/>
+          <t xml:space="preserve">11115
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">955
+</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
+</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4668
+</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6555,144 +6848,144 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22820
+          <t xml:space="preserve">4970
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19818
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">006
+</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">152
 </t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2862
-</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1801
-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">313
-</t>
-        </is>
-      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">9228
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9668
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -6708,137 +7001,137 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4970
-</t>
-        </is>
-      </c>
+      <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">14 5 9
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">585
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 140
+</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1 17 5
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1111511
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">778
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
@@ -626,122 +626,102 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9187
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
@@ -762,146 +742,122 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2939
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1535
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -918,144 +874,122 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">508
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1072,146 +1006,122 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>403</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1228,145 +1138,122 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2298
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>509</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>511</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>664</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1383,141 +1270,112 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11185
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>9 21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">511
-</t>
-        </is>
-      </c>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">734
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">002
-</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1664
-</t>
-        </is>
-      </c>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>897</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr"/>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1532,141 +1390,122 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">445
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97 9
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,26 +1527,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1717,44 +1552,37 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1764,26 +1592,22 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406491
-</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1791,36 +1615,11 @@
           <t>551</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">341
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6817
-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57175
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804940
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
+      <c r="X11" s="2" t="n"/>
+      <c r="Y11" s="2" t="n"/>
+      <c r="Z11" s="2" t="n"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1835,110 +1634,92 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
-</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr"/>
@@ -1950,8 +1731,7 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1961,8 +1741,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1979,146 +1758,122 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>945</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2135,146 +1890,122 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3240
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>949</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2291,146 +2022,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079
-</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0911
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2447,14 +2154,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1475
-</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2464,20 +2169,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1644
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2487,20 +2189,17 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2510,20 +2209,17 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11404
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2533,8 +2229,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2544,44 +2239,37 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3945
-</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>843</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
-</t>
+          <t>786</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12088
-</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2598,140 +2286,117 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2950
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">088
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28 14
-</t>
+          <t>12 14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2695
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>789</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2753,26 +2418,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4283
-</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2782,20 +2443,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2805,26 +2463,22 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -2835,14 +2489,12 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2852,8 +2504,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2863,14 +2514,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1701
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2880,8 +2529,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2898,146 +2546,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2149
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">540
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3054,38 +2678,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3095,20 +2713,17 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -3118,80 +2733,67 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3208,146 +2810,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
-</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
+          <t>908</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3364,134 +2942,112 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3501,8 +3057,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3524,39 +3079,33 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3566,14 +3115,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3583,50 +3130,42 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1090
-</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
-</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>913</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3641,14 +3180,12 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9295
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3665,146 +3202,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10434
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3821,26 +3334,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3865,51 +3374,43 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1842
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3924,14 +3425,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
@@ -3941,14 +3440,12 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3965,146 +3462,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1846
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4121,141 +3594,118 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7170
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4272,98 +3722,82 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -4373,44 +3807,37 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
-</t>
+          <t>728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4427,146 +3854,122 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2898
-</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4583,21 +3986,18 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16099
-</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11298
-</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4607,39 +4007,33 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
-</t>
+          <t>666</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>717</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4654,62 +4048,52 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610
-</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410
-</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4726,136 +4110,114 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2144
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4872,33 +4234,28 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4908,20 +4265,17 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4931,80 +4285,67 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5021,146 +4362,122 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14828
-</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1848
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5177,14 +4494,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4828
-</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5194,122 +4509,102 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11095
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z34" s="2" t="n"/>
@@ -5327,32 +4622,27 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94928
-</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5367,104 +4657,87 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2945
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6008
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>755</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5481,146 +4754,122 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94989
-</t>
+          <t>989</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2942
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1881
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>551</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5637,14 +4886,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21928
-</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -5659,110 +4906,89 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
-</t>
+          <t>533</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">757
-</t>
+          <t>757</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7112
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">716
-</t>
-        </is>
-      </c>
+          <t>027</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2348
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
-</t>
+          <t>804</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4098
-</t>
+          <t>095</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5784,50 +5010,42 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">438
-</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -5838,86 +5056,72 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>627</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5934,69 +5138,54 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">395953
-</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>016</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -6006,32 +5195,27 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -6042,14 +5226,12 @@
       <c r="V39" s="2" t="inlineStr"/>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -6081,32 +5263,27 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -6121,98 +5298,82 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4084
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6229,146 +5390,122 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401
-</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>889</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6385,146 +5522,122 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6541,141 +5654,122 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571
-</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1354
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr"/>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1867
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6690,148 +5784,116 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29830
-</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1836
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53409
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3510
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11115
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4668
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6848,145 +5910,122 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4970
-</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>919</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>690</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>959</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7001,138 +6040,124 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 5 9
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 140
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 17 5
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111511
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr"/>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1006,69 +1006,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
           <t>08</t>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9 21</t>
+          <t>22 95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>715</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>463</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>145</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>832</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2286,22 +2286,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12 14</t>
+          <t>0 14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>102</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>021</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>220</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>613</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>160</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>929</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>157</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>338</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>212</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>792</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>878</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>181 1</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>723</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>112</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>266</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>140</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>176</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>790</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>152</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5166,7 +5166,11 @@
           <t>120</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -5175,12 +5179,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>288</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5263,7 +5267,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5278,7 +5282,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5313,7 +5317,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5363,7 +5367,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5400,7 +5404,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5480,7 +5484,7 @@
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5490,7 +5494,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
@@ -5532,7 +5536,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5572,7 +5576,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>226</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5627,12 +5631,12 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5709,7 +5713,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5749,12 +5753,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
@@ -5837,7 +5841,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5858,7 +5862,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -5920,7 +5924,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5965,7 +5969,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>918</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5980,7 +5984,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>137</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -6010,7 +6014,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
@@ -6020,7 +6024,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -6062,7 +6066,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -6082,7 +6086,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6092,7 +6096,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>080</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -6147,12 +6151,12 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/601/Top_Excel_with_OCR_Results.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>388</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>224</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22 95</t>
+          <t>2 25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>02</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>20</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>835</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>248</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>230</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>202</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>021</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>170</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>09</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>54</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>165</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>913</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3099,13 +3099,13 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>643</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>913</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3737,69 +3737,69 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
           <t>415</t>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>838</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>181 1</t>
+          <t>181 2</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>286</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -5166,11 +5166,7 @@
           <t>120</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -5179,17 +5175,17 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>301</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -5282,7 +5278,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5317,7 +5313,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -5367,12 +5363,12 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5404,7 +5400,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5449,7 +5445,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>198</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -5494,7 +5490,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
@@ -5576,7 +5572,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>133</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5636,7 +5632,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5841,7 +5837,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5862,7 +5858,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -5914,7 +5910,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -6014,7 +6010,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>955</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
@@ -6086,7 +6082,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6096,7 +6092,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>080</t>
+          <t>084</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -6151,7 +6147,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -6161,7 +6157,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
